--- a/berlin_conservatories_1900.xlsx
+++ b/berlin_conservatories_1900.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\marten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFE5829-6844-4CC2-93BD-1C69949193FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAE641B-B6E1-42F0-9E03-C073C17CD1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-2055" windowWidth="29040" windowHeight="17520" xr2:uid="{5821C977-7948-43DB-918E-30E5E502D48B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="379">
   <si>
     <t>Akademie für Musik John Petersen</t>
   </si>
@@ -1170,6 +1170,9 @@
   </si>
   <si>
     <t>Königliche Akademie der Künste</t>
+  </si>
+  <si>
+    <t>Berlin</t>
   </si>
 </sst>
 </file>
@@ -1673,6 +1676,9 @@
       <c r="G2" s="12" t="s">
         <v>6</v>
       </c>
+      <c r="I2" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q2" s="12">
         <v>1911</v>
       </c>
@@ -1702,6 +1708,9 @@
       <c r="G3" s="12" t="s">
         <v>6</v>
       </c>
+      <c r="I3" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q3" s="12">
         <v>1914</v>
       </c>
@@ -1731,6 +1740,9 @@
       <c r="G4" s="12" t="s">
         <v>32</v>
       </c>
+      <c r="I4" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q4" s="12" t="s">
         <v>81</v>
       </c>
@@ -1760,6 +1772,9 @@
       <c r="G5" s="12" t="s">
         <v>1</v>
       </c>
+      <c r="I5" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J5" s="12" t="s">
         <v>60</v>
       </c>
@@ -1792,6 +1807,9 @@
       <c r="G6" s="12" t="s">
         <v>2</v>
       </c>
+      <c r="I6" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q6" s="12">
         <v>1914</v>
       </c>
@@ -1821,6 +1839,9 @@
       <c r="G7" s="12" t="s">
         <v>33</v>
       </c>
+      <c r="I7" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q7" s="12">
         <v>1911</v>
       </c>
@@ -1850,6 +1871,9 @@
       <c r="G8" s="12" t="s">
         <v>33</v>
       </c>
+      <c r="I8" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q8" s="12">
         <v>1914</v>
       </c>
@@ -1879,6 +1903,9 @@
       <c r="G9" s="12" t="s">
         <v>34</v>
       </c>
+      <c r="I9" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J9" s="12" t="s">
         <v>61</v>
       </c>
@@ -1911,6 +1938,9 @@
       <c r="G10" s="12" t="s">
         <v>35</v>
       </c>
+      <c r="I10" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q10" s="12">
         <v>1909</v>
       </c>
@@ -1940,6 +1970,9 @@
       <c r="G11" s="12" t="s">
         <v>2</v>
       </c>
+      <c r="I11" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q11" s="12">
         <v>1914</v>
       </c>
@@ -1969,6 +2002,9 @@
       <c r="G12" s="12" t="s">
         <v>36</v>
       </c>
+      <c r="I12" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q12" s="12">
         <v>1914</v>
       </c>
@@ -1998,6 +2034,9 @@
       <c r="G13" s="12" t="s">
         <v>4</v>
       </c>
+      <c r="I13" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q13" s="12">
         <v>1914</v>
       </c>
@@ -2027,6 +2066,9 @@
       <c r="G14" s="12" t="s">
         <v>37</v>
       </c>
+      <c r="I14" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q14" s="12" t="s">
         <v>85</v>
       </c>
@@ -2062,6 +2104,9 @@
       <c r="G15" s="12" t="s">
         <v>38</v>
       </c>
+      <c r="I15" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="P15" s="12" t="s">
         <v>370</v>
       </c>
@@ -2100,6 +2145,9 @@
       <c r="G16" s="12" t="s">
         <v>39</v>
       </c>
+      <c r="I16" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q16" s="12">
         <v>1914</v>
       </c>
@@ -2129,6 +2177,9 @@
       <c r="G17" s="12" t="s">
         <v>40</v>
       </c>
+      <c r="I17" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J17" s="12" t="s">
         <v>63</v>
       </c>
@@ -2161,6 +2212,9 @@
       <c r="G18" s="12" t="s">
         <v>41</v>
       </c>
+      <c r="I18" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J18" s="12" t="s">
         <v>64</v>
       </c>
@@ -2199,6 +2253,9 @@
       <c r="G19" s="12" t="s">
         <v>1</v>
       </c>
+      <c r="I19" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J19" s="12" t="s">
         <v>64</v>
       </c>
@@ -2240,6 +2297,9 @@
       <c r="G20" s="12" t="s">
         <v>39</v>
       </c>
+      <c r="I20" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J20" s="12" t="s">
         <v>70</v>
       </c>
@@ -2281,6 +2341,9 @@
       <c r="G21" s="12" t="s">
         <v>50</v>
       </c>
+      <c r="I21" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J21" s="12" t="s">
         <v>70</v>
       </c>
@@ -2322,6 +2385,9 @@
       <c r="G22" s="12" t="s">
         <v>44</v>
       </c>
+      <c r="I22" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J22" s="12">
         <v>1881</v>
       </c>
@@ -2357,6 +2423,9 @@
       <c r="G23" s="12" t="s">
         <v>1</v>
       </c>
+      <c r="I23" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J23" s="12" t="s">
         <v>65</v>
       </c>
@@ -2392,6 +2461,9 @@
       <c r="G24" s="12" t="s">
         <v>42</v>
       </c>
+      <c r="I24" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J24" s="12" t="s">
         <v>65</v>
       </c>
@@ -2430,6 +2502,9 @@
       <c r="G25" s="12" t="s">
         <v>43</v>
       </c>
+      <c r="I25" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J25" s="12" t="s">
         <v>66</v>
       </c>
@@ -2471,6 +2546,9 @@
       <c r="G26" s="12" t="s">
         <v>44</v>
       </c>
+      <c r="I26" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q26" s="12" t="s">
         <v>85</v>
       </c>
@@ -2506,6 +2584,9 @@
       <c r="G27" s="12" t="s">
         <v>44</v>
       </c>
+      <c r="I27" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="R27" s="12" t="s">
         <v>94</v>
       </c>
@@ -2538,6 +2619,9 @@
       <c r="G28" s="12" t="s">
         <v>45</v>
       </c>
+      <c r="I28" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J28" s="12" t="s">
         <v>67</v>
       </c>
@@ -2567,6 +2651,9 @@
       <c r="G29" s="12" t="s">
         <v>46</v>
       </c>
+      <c r="I29" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q29" s="12">
         <v>1909</v>
       </c>
@@ -2596,6 +2683,9 @@
       <c r="G30" s="12" t="s">
         <v>47</v>
       </c>
+      <c r="I30" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q30" s="12" t="s">
         <v>85</v>
       </c>
@@ -2625,6 +2715,9 @@
       <c r="G31" s="12" t="s">
         <v>6</v>
       </c>
+      <c r="I31" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q31" s="12">
         <v>1914</v>
       </c>
@@ -2654,6 +2747,9 @@
       <c r="G32" s="12" t="s">
         <v>32</v>
       </c>
+      <c r="I32" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q32" s="12">
         <v>1909</v>
       </c>
@@ -2683,6 +2779,9 @@
       <c r="G33" s="12" t="s">
         <v>32</v>
       </c>
+      <c r="I33" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q33" s="12" t="s">
         <v>85</v>
       </c>
@@ -2712,6 +2811,9 @@
       <c r="G34" s="12" t="s">
         <v>48</v>
       </c>
+      <c r="I34" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J34" s="12" t="s">
         <v>68</v>
       </c>
@@ -2744,6 +2846,9 @@
       <c r="G35" s="12" t="s">
         <v>49</v>
       </c>
+      <c r="I35" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J35" s="12" t="s">
         <v>69</v>
       </c>
@@ -2779,6 +2884,9 @@
       <c r="G36" s="12" t="s">
         <v>6</v>
       </c>
+      <c r="I36" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J36" s="12" t="s">
         <v>69</v>
       </c>
@@ -2811,6 +2919,9 @@
       <c r="G37" s="12" t="s">
         <v>44</v>
       </c>
+      <c r="I37" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J37" s="12" t="s">
         <v>71</v>
       </c>
@@ -2846,6 +2957,9 @@
       <c r="G38" s="12" t="s">
         <v>44</v>
       </c>
+      <c r="I38" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="P38" s="12" t="s">
         <v>351</v>
       </c>
@@ -2878,6 +2992,9 @@
       <c r="G39" s="12" t="s">
         <v>51</v>
       </c>
+      <c r="I39" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q39" s="12">
         <v>1914</v>
       </c>
@@ -2907,6 +3024,9 @@
       <c r="G40" s="12" t="s">
         <v>1</v>
       </c>
+      <c r="I40" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q40" s="12" t="s">
         <v>85</v>
       </c>
@@ -2936,6 +3056,9 @@
       <c r="G41" s="12" t="s">
         <v>52</v>
       </c>
+      <c r="I41" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J41" s="12" t="s">
         <v>72</v>
       </c>
@@ -2968,6 +3091,9 @@
       <c r="G42" s="12" t="s">
         <v>48</v>
       </c>
+      <c r="I42" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q42" s="12">
         <v>1909</v>
       </c>
@@ -2997,6 +3123,9 @@
       <c r="G43" s="12" t="s">
         <v>53</v>
       </c>
+      <c r="I43" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q43" s="12">
         <v>1914</v>
       </c>
@@ -3026,6 +3155,9 @@
       <c r="G44" s="12" t="s">
         <v>33</v>
       </c>
+      <c r="I44" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q44" s="12" t="s">
         <v>85</v>
       </c>
@@ -3055,6 +3187,9 @@
       <c r="G45" s="12" t="s">
         <v>40</v>
       </c>
+      <c r="I45" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q45" s="12">
         <v>1914</v>
       </c>
@@ -3084,6 +3219,9 @@
       <c r="G46" s="12" t="s">
         <v>50</v>
       </c>
+      <c r="I46" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J46" s="12" t="s">
         <v>73</v>
       </c>
@@ -3119,6 +3257,9 @@
       <c r="F47" s="12" t="s">
         <v>287</v>
       </c>
+      <c r="I47" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J47" s="12" t="s">
         <v>74</v>
       </c>
@@ -3151,6 +3292,9 @@
       <c r="G48" s="12" t="s">
         <v>54</v>
       </c>
+      <c r="I48" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J48" s="12" t="s">
         <v>75</v>
       </c>
@@ -3183,6 +3327,9 @@
       <c r="G49" s="12" t="s">
         <v>55</v>
       </c>
+      <c r="I49" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="L49" s="12" t="s">
         <v>62</v>
       </c>
@@ -3212,6 +3359,9 @@
       <c r="G50" s="12" t="s">
         <v>82</v>
       </c>
+      <c r="I50" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="P50" s="12" t="s">
         <v>89</v>
       </c>
@@ -3244,6 +3394,9 @@
       <c r="G51" s="12" t="s">
         <v>2</v>
       </c>
+      <c r="I51" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="P51" s="12" t="s">
         <v>337</v>
       </c>
@@ -3276,6 +3429,9 @@
       <c r="G52" s="12" t="s">
         <v>35</v>
       </c>
+      <c r="I52" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J52" s="12" t="s">
         <v>76</v>
       </c>
@@ -3308,6 +3464,9 @@
       <c r="G53" s="12" t="s">
         <v>50</v>
       </c>
+      <c r="I53" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J53" s="12" t="s">
         <v>76</v>
       </c>
@@ -3340,6 +3499,9 @@
       <c r="G54" s="12" t="s">
         <v>33</v>
       </c>
+      <c r="I54" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J54" s="12" t="s">
         <v>77</v>
       </c>
@@ -3375,6 +3537,9 @@
       <c r="G55" s="12" t="s">
         <v>48</v>
       </c>
+      <c r="I55" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J55" s="12" t="s">
         <v>77</v>
       </c>
@@ -3410,6 +3575,9 @@
       <c r="G56" s="12" t="s">
         <v>56</v>
       </c>
+      <c r="I56" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q56" s="12">
         <v>1909</v>
       </c>
@@ -3439,6 +3607,9 @@
       <c r="G57" s="12" t="s">
         <v>83</v>
       </c>
+      <c r="I57" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q57" s="12">
         <v>1911</v>
       </c>
@@ -3468,6 +3639,9 @@
       <c r="G58" s="12" t="s">
         <v>57</v>
       </c>
+      <c r="I58" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q58" s="12" t="s">
         <v>86</v>
       </c>
@@ -3497,6 +3671,9 @@
       <c r="G59" s="12" t="s">
         <v>58</v>
       </c>
+      <c r="I59" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J59" s="12" t="s">
         <v>78</v>
       </c>
@@ -3529,6 +3706,9 @@
       <c r="G60" s="12" t="s">
         <v>1</v>
       </c>
+      <c r="I60" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="J60" s="12" t="s">
         <v>78</v>
       </c>
@@ -3561,6 +3741,9 @@
       <c r="G61" s="12" t="s">
         <v>59</v>
       </c>
+      <c r="I61" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="Q61" s="12" t="s">
         <v>86</v>
       </c>
@@ -3589,6 +3772,9 @@
       </c>
       <c r="G62" s="12" t="s">
         <v>6</v>
+      </c>
+      <c r="I62" s="12" t="s">
+        <v>378</v>
       </c>
       <c r="Q62" s="12" t="s">
         <v>85</v>
